--- a/artfynd/A 10048-2026 artfynd.xlsx
+++ b/artfynd/A 10048-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050892</v>
       </c>
       <c r="B2" t="n">
-        <v>83248</v>
+        <v>83249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132050926</v>
       </c>
       <c r="B3" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132050916</v>
       </c>
       <c r="B4" t="n">
-        <v>58065</v>
+        <v>58066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>132050897</v>
       </c>
       <c r="B5" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>132050896</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10048-2026 artfynd.xlsx
+++ b/artfynd/A 10048-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050892</v>
       </c>
       <c r="B2" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132050926</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132050916</v>
       </c>
       <c r="B4" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>132050897</v>
       </c>
       <c r="B5" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>132050896</v>
       </c>
       <c r="B6" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10048-2026 artfynd.xlsx
+++ b/artfynd/A 10048-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050892</v>
       </c>
       <c r="B2" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132050926</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132050916</v>
       </c>
       <c r="B4" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,10 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132050897</v>
+        <v>132050896</v>
       </c>
       <c r="B5" t="n">
-        <v>57912</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -999,21 +999,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479816</v>
+        <v>479811</v>
       </c>
       <c r="R5" t="n">
-        <v>6993153</v>
+        <v>6993089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,11 +1059,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,10 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050896</v>
+        <v>132050897</v>
       </c>
       <c r="B6" t="n">
-        <v>91846</v>
+        <v>57914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,21 +1096,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479811</v>
+        <v>479816</v>
       </c>
       <c r="R6" t="n">
-        <v>6993089</v>
+        <v>6993153</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,6 +1156,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 10048-2026 artfynd.xlsx
+++ b/artfynd/A 10048-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132050892</v>
+        <v>132050896</v>
       </c>
       <c r="B2" t="n">
-        <v>83307</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479964</v>
+        <v>479811</v>
       </c>
       <c r="R2" t="n">
-        <v>6992941</v>
+        <v>6993089</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132050926</v>
+        <v>132616036</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479875</v>
+        <v>479905</v>
       </c>
       <c r="R3" t="n">
-        <v>6992824</v>
+        <v>6992806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,57 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132050916</v>
+        <v>132050926</v>
       </c>
       <c r="B4" t="n">
-        <v>58114</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479832</v>
+        <v>479875</v>
       </c>
       <c r="R4" t="n">
-        <v>6992826</v>
+        <v>6992824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2 st, födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,45 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132050897</v>
+        <v>132616086</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479816</v>
+        <v>480006</v>
       </c>
       <c r="R5" t="n">
-        <v>6993153</v>
+        <v>6992847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,17 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,45 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050896</v>
+        <v>132616088</v>
       </c>
       <c r="B6" t="n">
-        <v>91909</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartsjöarna, Jmt</t>
+          <t>Måläng, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479811</v>
+        <v>480021</v>
       </c>
       <c r="R6" t="n">
-        <v>6993089</v>
+        <v>6992811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1187,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132616036</v>
+        <v>132050892</v>
       </c>
       <c r="B7" t="n">
-        <v>91918</v>
+        <v>83358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1198,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479905</v>
+        <v>479964</v>
       </c>
       <c r="R7" t="n">
-        <v>6992806</v>
+        <v>6992941</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1252,12 +1225,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132616082</v>
+        <v>132616045</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>80493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479888</v>
+        <v>480012</v>
       </c>
       <c r="R8" t="n">
-        <v>6992802</v>
+        <v>6992800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Över 50 plantor, utspritt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,45 +1359,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132616080</v>
+        <v>132050897</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479874</v>
+        <v>479816</v>
       </c>
       <c r="R9" t="n">
-        <v>6992806</v>
+        <v>6993153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,17 +1424,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Över 20 plantor, utspritt</t>
+          <t>Ringhack, äldre, på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,45 +1461,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132616063</v>
+        <v>132050916</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Måläng, Jmt</t>
+          <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480030</v>
+        <v>479832</v>
       </c>
       <c r="R10" t="n">
-        <v>6992852</v>
+        <v>6992826</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,17 +1538,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 10 st</t>
+          <t>2 st, födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132616069</v>
+        <v>132616063</v>
       </c>
       <c r="B11" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1625,10 +1610,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480033</v>
+        <v>480030</v>
       </c>
       <c r="R11" t="n">
-        <v>6992856</v>
+        <v>6992852</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1650,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca 20 plantor utspridda</t>
+          <t>Ca 10 st</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,7 +1680,7 @@
         <v>132616065</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132616086</v>
+        <v>132616069</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480006</v>
+        <v>480033</v>
       </c>
       <c r="R13" t="n">
-        <v>6992847</v>
+        <v>6992856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,6 +1852,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor utspridda</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1888,6 +1878,210 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132616080</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Måläng, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>479874</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6992806</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Över 20 plantor, utspritt</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132616082</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Måläng, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>479888</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6992802</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Över 50 plantor, utspritt</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10048-2026 artfynd.xlsx
+++ b/artfynd/A 10048-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616036</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050926</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616086</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616088</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050892</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616045</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050916</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616063</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616065</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1679,6 +1729,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616069</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1781,6 +1836,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616080</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1883,6 +1943,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132616082</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1980,6 +2045,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050896</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2082,8 +2152,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050897</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>